--- a/data/import/ystech.xlsx
+++ b/data/import/ystech.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,11 @@
           <t>pub</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -593,6 +598,11 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/direct-label/</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -664,6 +674,11 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/direct-label/</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -735,6 +750,11 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/direct-label/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -806,6 +826,11 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/direct-label/</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -877,6 +902,11 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -948,6 +978,11 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1024,6 +1059,11 @@
       <c r="U8" t="n">
         <v>1</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1095,6 +1135,11 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1166,6 +1211,11 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1237,6 +1287,11 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1313,6 +1368,11 @@
       <c r="U12" t="n">
         <v>1</v>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1384,6 +1444,11 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1455,6 +1520,11 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1526,6 +1596,11 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1597,6 +1672,11 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-label/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1668,6 +1748,11 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1739,6 +1824,11 @@
       <c r="U18" t="n">
         <v>0</v>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1810,6 +1900,11 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1881,6 +1976,11 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1952,6 +2052,11 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2023,6 +2128,11 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2094,6 +2204,11 @@
       <c r="U23" t="n">
         <v>0</v>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2165,6 +2280,11 @@
       <c r="U24" t="n">
         <v>0</v>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2236,6 +2356,11 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2307,6 +2432,11 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2383,6 +2513,11 @@
       <c r="U27" t="n">
         <v>1</v>
       </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2458,6 +2593,11 @@
       </c>
       <c r="U28" t="n">
         <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>https://www.heatprooflabel.com/products/management-tag/</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/import/ystech.xlsx
+++ b/data/import/ystech.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,11 @@
           <t>tds</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
